--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.89647</v>
+        <v>16.80556</v>
       </c>
       <c r="D2" t="n">
-        <v>16.66747</v>
+        <v>16.5823</v>
       </c>
       <c r="E2" t="n">
-        <v>16.70184</v>
+        <v>16.59724</v>
       </c>
       <c r="F2" t="n">
-        <v>42.36458</v>
+        <v>41.83483</v>
       </c>
       <c r="G2" t="n">
         <v>0.05049</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7955</v>
+        <v>1.83188</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.75139</v>
+        <v>16.70684</v>
       </c>
       <c r="D3" t="n">
-        <v>16.46066</v>
+        <v>16.37397</v>
       </c>
       <c r="E3" t="n">
-        <v>16.89841</v>
+        <v>16.67225</v>
       </c>
       <c r="F3" t="n">
-        <v>43.20119</v>
+        <v>41.95159</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05112</v>
+        <v>0.052</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80991</v>
+        <v>1.85906</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.86927</v>
+        <v>16.80681</v>
       </c>
       <c r="D4" t="n">
-        <v>16.57024</v>
+        <v>16.54949</v>
       </c>
       <c r="E4" t="n">
-        <v>16.50341</v>
+        <v>16.56671</v>
       </c>
       <c r="F4" t="n">
-        <v>42.84003</v>
+        <v>41.84378</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05097</v>
+        <v>0.05118</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84981</v>
+        <v>1.83697</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.66103</v>
+        <v>16.48155</v>
       </c>
       <c r="D6" t="n">
-        <v>16.26893</v>
+        <v>16.17858</v>
       </c>
       <c r="E6" t="n">
-        <v>15.99835</v>
+        <v>16.31488</v>
       </c>
       <c r="F6" t="n">
-        <v>21.58599</v>
+        <v>21.79857</v>
       </c>
       <c r="G6" t="n">
-        <v>33.68774</v>
+        <v>33.72138</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.75822</v>
+        <v>16.73152</v>
       </c>
       <c r="D7" t="n">
-        <v>16.157</v>
+        <v>15.92884</v>
       </c>
       <c r="E7" t="n">
-        <v>16.82541</v>
+        <v>16.49456</v>
       </c>
       <c r="F7" t="n">
-        <v>21.8671</v>
+        <v>21.56485</v>
       </c>
       <c r="G7" t="n">
-        <v>34.13329</v>
+        <v>34.19441</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.96696</v>
+        <v>16.84063</v>
       </c>
       <c r="D8" t="n">
-        <v>15.97412</v>
+        <v>16.14079</v>
       </c>
       <c r="E8" t="n">
-        <v>16.67134</v>
+        <v>16.34233</v>
       </c>
       <c r="F8" t="n">
-        <v>21.85787</v>
+        <v>21.57532</v>
       </c>
       <c r="G8" t="n">
-        <v>33.93258</v>
+        <v>34.17841</v>
       </c>
     </row>
   </sheetData>
